--- a/3_Statement_of_Applicability/MT-ISMS-SOA-001_v1.2_statement-of-applicability.xlsx
+++ b/3_Statement_of_Applicability/MT-ISMS-SOA-001_v1.2_statement-of-applicability.xlsx
@@ -4506,8 +4506,10 @@
       </c>
     </row>
     <row r="6" spans="2:5" ht="85" x14ac:dyDescent="0.2">
-      <c r="B6" s="27">
-        <v>1.1000000000000001</v>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
       </c>
       <c r="C6" s="25" t="s">
         <v>3</v>

--- a/3_Statement_of_Applicability/MT-ISMS-SOA-001_v1.2_statement-of-applicability.xlsx
+++ b/3_Statement_of_Applicability/MT-ISMS-SOA-001_v1.2_statement-of-applicability.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="487">
   <si>
     <t>MunichTech GmbH</t>
   </si>
@@ -50,7 +50,7 @@
     <t>Effective Date</t>
   </si>
   <si>
-    <t>[Date]</t>
+    <t/>
   </si>
   <si>
     <t>Austin Bond, Junior GRC Consultant</t>
@@ -102,7 +102,7 @@
     <t>Approved By</t>
   </si>
   <si>
-    <t>[Senior GRC Partner Name], CISM, ISO LA</t>
+    <t>Dr. Andreas Kellermann, CISM, ISO LA</t>
   </si>
   <si>
     <t>Operations Manager</t>
@@ -1500,6 +1500,24 @@
   </si>
   <si>
     <t>Citation correction: BaFin BAIT (withdrawn 17 January 2025) replaced by DORA (Reg. (EU) 2022/2554). No control applicability, implementation status or risk linkage changed.</t>
+  </si>
+  <si>
+    <t>21 October 2026</t>
+  </si>
+  <si>
+    <t>4 November 2025</t>
+  </si>
+  <si>
+    <t>11 February 2026</t>
+  </si>
+  <si>
+    <t>AWS GuardDuty provides automated threat intelligence using managed detection models. Financial-sector STIX/TAXII feeds are integrated directly into the Splunk SIEM, live since 15 June 2026 under the action approved at the FY2026 Management Review (MT-ISMS-MRA-001, Agenda Item 7; change reference PR #418). Evidence: Splunk feed configuration export and ingestion dashboard screenshot, retained in the ISMS evidence register.</t>
+  </si>
+  <si>
+    <t>Acceptable Use Policy established. Endpoint monitoring and web filtering restrictions have been formally approved by the Works Council (Betriebsrat) via Betriebsvereinbarung MT-WorksCouncil-CrowdStrike-v1.2. Ref: MT-POL-007</t>
+  </si>
+  <si>
+    <t>Citation correction: BaFin BAIT (withdrawn 17 January 2025) replaced by DORA (Reg. (EU) 2022/2554). No control applicability or risk linkage changed; A.5.7 additionally gained a completion record for the STIX/TAXII feed integration and remains Fully Implemented.</t>
   </si>
 </sst>
 </file>
@@ -2220,7 +2238,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>3</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
@@ -2441,7 +2459,7 @@
         <v>31</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>114</v>
+        <v>484</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>121</v>
@@ -2512,7 +2530,7 @@
         <v>31</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>117</v>
+        <v>485</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>124</v>
@@ -4496,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>3</v>
+        <v>482</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>462</v>
@@ -4512,7 +4530,7 @@
         </is>
       </c>
       <c r="C6" s="25" t="s">
-        <v>3</v>
+        <v>483</v>
       </c>
       <c r="D6" s="25" t="s">
         <v>462</v>
@@ -4526,13 +4544,13 @@
         <v>1.2</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>3</v>
+        <v>481</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>462</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
